--- a/exports/POWERINDIA_full_report.xlsx
+++ b/exports/POWERINDIA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.59</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44602.55208333334</v>
+        <v>44603.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>2976.15</v>
+        <v>2874</v>
       </c>
       <c r="I2" t="n">
         <v>2927.339521965561</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K2" t="n">
-        <v>21.13</v>
+        <v>16.97</v>
       </c>
       <c r="L2" t="n">
         <v>1.1</v>
@@ -555,7 +578,7 @@
         <v>1.37</v>
       </c>
       <c r="N2" t="n">
-        <v>4.17</v>
+        <v>5.08</v>
       </c>
       <c r="O2" t="n">
         <v>0.13</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>13.86</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44614.55208333334</v>
+        <v>44615.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>3175</v>
+        <v>3266.35</v>
       </c>
       <c r="I3" t="n">
         <v>3182.414884068701</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.47</v>
+        <v>-13.65</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>16.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.3</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.49</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>3429</v>
+        <v>3257</v>
       </c>
       <c r="I4" t="n">
         <v>3257.885538585072</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55</v>
+        <v>55.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>4.98</v>
+        <v>-0.29</v>
       </c>
       <c r="L4" t="n">
         <v>8.16</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.6</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44697.55208333334</v>
+        <v>44698.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>3060.9</v>
+        <v>3154</v>
       </c>
       <c r="I5" t="n">
         <v>3115.455356018431</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>6.02</v>
+        <v>3.16</v>
       </c>
       <c r="L5" t="n">
         <v>5.91</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.56</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>3273.1</v>
+        <v>3203.1</v>
       </c>
       <c r="I6" t="n">
         <v>3207.196657280959</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>3.78</v>
+        <v>1.56</v>
       </c>
       <c r="L6" t="n">
         <v>3.93</v>
@@ -783,7 +854,7 @@
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>4.72</v>
       </c>
       <c r="O6" t="n">
         <v>2.62</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.98</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44747.38541666666</v>
+        <v>44747.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>3203.8</v>
+        <v>3247</v>
       </c>
       <c r="I7" t="n">
         <v>3224.537892388409</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.02</v>
+        <v>-1.37</v>
       </c>
       <c r="L7" t="n">
         <v>3.92</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.4</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44763.55208333334</v>
+        <v>44764.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>3449</v>
+        <v>3216.9</v>
       </c>
       <c r="I8" t="n">
         <v>3372.003759407147</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>6.22</v>
+        <v>-0.93</v>
       </c>
       <c r="L8" t="n">
         <v>1.87</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.87</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
         <v>3.72</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>12.12</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44774.55208333334</v>
+        <v>44775.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>3307.1</v>
+        <v>3405</v>
       </c>
       <c r="I9" t="n">
         <v>3404.113975193384</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.8</v>
+        <v>-5.85</v>
       </c>
       <c r="L9" t="n">
-        <v>4.36</v>
+        <v>6.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.86</v>
+        <v>4.05</v>
       </c>
       <c r="O9" t="n">
         <v>-8</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44784.55208333334</v>
+        <v>44785.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>3302.2</v>
+        <v>3245.05</v>
       </c>
       <c r="I10" t="n">
         <v>3255.244776398071</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.02</v>
+        <v>-4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>4.07</v>
+        <v>4.89</v>
       </c>
       <c r="M10" t="n">
         <v>0.01</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>3421</v>
+        <v>3586.55</v>
       </c>
       <c r="I11" t="n">
         <v>3462.615703459349</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.42</v>
+        <v>-10.52</v>
       </c>
       <c r="L11" t="n">
-        <v>7.21</v>
+        <v>13.4</v>
       </c>
       <c r="M11" t="n">
         <v>0.88</v>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="O11" t="n">
         <v>-1.61</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.49</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3532</v>
+        <v>3445.05</v>
       </c>
       <c r="I12" t="n">
         <v>3506.817972872843</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.52</v>
+        <v>-3.95</v>
       </c>
       <c r="L12" t="n">
         <v>4.61</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.02</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44902.55208333334</v>
+        <v>44903.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>3009.45</v>
+        <v>3050</v>
       </c>
       <c r="I13" t="n">
         <v>3049.888947491395</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>82.16666666666667</v>
+        <v>83</v>
       </c>
       <c r="K13" t="n">
-        <v>12.64</v>
+        <v>11.47</v>
       </c>
       <c r="L13" t="n">
         <v>5.68</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.11</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44946.55208333334</v>
+        <v>44949.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>3229.95</v>
+        <v>3167.8</v>
       </c>
       <c r="I14" t="n">
         <v>3205.27840646541</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K14" t="n">
-        <v>5.9</v>
+        <v>3.86</v>
       </c>
       <c r="L14" t="n">
         <v>1.41</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>5.64</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44980.55208333334</v>
+        <v>44981.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>3170</v>
+        <v>3265</v>
       </c>
       <c r="I15" t="n">
         <v>3177.23986470615</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.07</v>
       </c>
       <c r="L15" t="n">
-        <v>2.44</v>
+        <v>3.19</v>
       </c>
       <c r="M15" t="n">
         <v>3.11</v>
       </c>
       <c r="N15" t="n">
-        <v>3.41</v>
+        <v>4.57</v>
       </c>
       <c r="O15" t="n">
         <v>-1.39</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.38</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44999.38541666666</v>
+        <v>44999.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>3375.15</v>
+        <v>3265</v>
       </c>
       <c r="I16" t="n">
         <v>3319.932978118486</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>3.48</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.27</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45036.38541666666</v>
+        <v>45036.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>3128</v>
+        <v>3199</v>
       </c>
       <c r="I17" t="n">
         <v>3188.000267228699</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>36.83333333333334</v>
+        <v>37</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="L17" t="n">
         <v>5.33</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.07</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45133.55208333334</v>
+        <v>45134.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>4054</v>
+        <v>4037.55</v>
       </c>
       <c r="I18" t="n">
         <v>4046.532770058395</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>97</v>
+        <v>97.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>26.73</v>
+        <v>26.21</v>
       </c>
       <c r="L18" t="n">
         <v>2.22</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>7.69</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45140.55208333334</v>
+        <v>45141.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>4015.05</v>
+        <v>4178.8</v>
       </c>
       <c r="I19" t="n">
         <v>4176.255963824909</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5600000000000001</v>
+        <v>-3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>2.29</v>
+        <v>3.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0.57</v>
+        <v>0.77</v>
       </c>
       <c r="N19" t="n">
-        <v>1.24</v>
+        <v>6.97</v>
       </c>
       <c r="O19" t="n">
         <v>-0.1</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.07</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45184.55208333334</v>
+        <v>45187.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>4345</v>
+        <v>4215.55</v>
       </c>
       <c r="I20" t="n">
         <v>4300.193838896861</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K20" t="n">
-        <v>3.98</v>
+        <v>0.88</v>
       </c>
       <c r="L20" t="n">
         <v>3.56</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45210.55208333334</v>
+        <v>45211.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>4108.5</v>
+        <v>4251</v>
       </c>
       <c r="I21" t="n">
         <v>4158.868176815221</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>2.54</v>
+        <v>-0.84</v>
       </c>
       <c r="L21" t="n">
         <v>2.99</v>
@@ -1638,7 +1889,7 @@
         <v>0.93</v>
       </c>
       <c r="N21" t="n">
-        <v>2.45</v>
+        <v>5.17</v>
       </c>
       <c r="O21" t="n">
         <v>-2.83</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.11</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>4550</v>
+        <v>4310</v>
       </c>
       <c r="I22" t="n">
         <v>4359.806864548132</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K22" t="n">
-        <v>7.03</v>
+        <v>1.39</v>
       </c>
       <c r="L22" t="n">
         <v>3.2</v>
@@ -1695,7 +1958,7 @@
         <v>0.49</v>
       </c>
       <c r="N22" t="n">
-        <v>1.51</v>
+        <v>4.86</v>
       </c>
       <c r="O22" t="n">
         <v>5.17</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.77</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45232.38541666666</v>
+        <v>45232.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>4368.9</v>
+        <v>4465</v>
       </c>
       <c r="I23" t="n">
         <v>4439.228985927085</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.37</v>
+        <v>-3.6</v>
       </c>
       <c r="L23" t="n">
         <v>5.9</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45314.55208333334</v>
+        <v>45315.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>5866</v>
+        <v>5650</v>
       </c>
       <c r="I24" t="n">
         <v>5709.271089483711</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>82</v>
+        <v>82.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>31.38</v>
+        <v>26.54</v>
       </c>
       <c r="L24" t="n">
         <v>3.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0.55</v>
+        <v>3.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="O24" t="n">
         <v>8.33</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>8.44</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45327.38541666666</v>
+        <v>45327.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>6055</v>
+        <v>6259</v>
       </c>
       <c r="I25" t="n">
         <v>6126.834503120764</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.17</v>
+        <v>-10.78</v>
       </c>
       <c r="L25" t="n">
-        <v>7.66</v>
+        <v>11.06</v>
       </c>
       <c r="M25" t="n">
         <v>1.78</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.26</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>11081</v>
+        <v>9667.1</v>
       </c>
       <c r="I26" t="n">
         <v>9923.06207399268</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>119</v>
+        <v>119.8333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>77.04000000000001</v>
+        <v>54.45</v>
       </c>
       <c r="L26" t="n">
         <v>8.32</v>
@@ -1923,7 +2234,7 @@
         <v>2.77</v>
       </c>
       <c r="N26" t="n">
-        <v>4.54</v>
+        <v>11.29</v>
       </c>
       <c r="O26" t="n">
         <v>10.15</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>22.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45457.55208333334</v>
+        <v>45461.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>11100</v>
+        <v>11433</v>
       </c>
       <c r="I27" t="n">
         <v>11345.3230507534</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-14.82</v>
+        <v>-18.27</v>
       </c>
       <c r="L27" t="n">
-        <v>15.84</v>
+        <v>19.86</v>
       </c>
       <c r="M27" t="n">
         <v>3.12</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.52</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45485.38541666666</v>
+        <v>45485.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>12600</v>
+        <v>12200</v>
       </c>
       <c r="I28" t="n">
         <v>12564.12928954121</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>10.21</v>
+        <v>6.71</v>
       </c>
       <c r="L28" t="n">
         <v>4.66</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>12.88</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45520.55208333334</v>
+        <v>45523.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>11800</v>
+        <v>12289.75</v>
       </c>
       <c r="I29" t="n">
         <v>12233.23402579485</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>3.28</v>
+        <v>-0.74</v>
       </c>
       <c r="L29" t="n">
         <v>3.88</v>
       </c>
       <c r="M29" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="N29" t="n">
         <v>7.02</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>10.92</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>11580</v>
+        <v>11319.2</v>
       </c>
       <c r="I30" t="n">
         <v>11420.27903475231</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.78</v>
+        <v>-7.9</v>
       </c>
       <c r="L30" t="n">
-        <v>7.21</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="N30" t="n">
         <v>3.89</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.34</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45547.38541666666</v>
+        <v>45547.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>12108.45</v>
+        <v>12306</v>
       </c>
       <c r="I31" t="n">
         <v>12263.0522173868</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.97</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>9.06</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>0.28</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.08</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>14889.95</v>
+        <v>14348.55</v>
       </c>
       <c r="I32" t="n">
         <v>14516.77062898926</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>39</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>16.6</v>
       </c>
       <c r="L32" t="n">
         <v>1.67</v>
@@ -2265,7 +2648,7 @@
         <v>1.02</v>
       </c>
       <c r="N32" t="n">
-        <v>4.38</v>
+        <v>7.32</v>
       </c>
       <c r="O32" t="n">
         <v>1.12</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>12.01</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45602.38541666666</v>
+        <v>45602.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>14403.7</v>
+        <v>14840</v>
       </c>
       <c r="I33" t="n">
         <v>14781.87426108688</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.38</v>
+        <v>-3.43</v>
       </c>
       <c r="L33" t="n">
-        <v>3.85</v>
+        <v>4.16</v>
       </c>
       <c r="M33" t="n">
         <v>1.4</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.58</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45607.55208333334</v>
+        <v>45608.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>13352.5</v>
+        <v>13005.05</v>
       </c>
       <c r="I34" t="n">
         <v>13129.47264601623</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-10.02</v>
+        <v>-12.36</v>
       </c>
       <c r="L34" t="n">
         <v>14.24</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>13.33</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45637.55208333334</v>
+        <v>45638.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>12649.95</v>
+        <v>13080.2</v>
       </c>
       <c r="I35" t="n">
         <v>12848.72205028255</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K35" t="n">
-        <v>2.73</v>
+        <v>-0.58</v>
       </c>
       <c r="L35" t="n">
         <v>3.73</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.5</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45665.55208333334</v>
+        <v>45666.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>14370.1</v>
+        <v>13860</v>
       </c>
       <c r="I36" t="n">
         <v>14054.94708888845</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K36" t="n">
-        <v>9.859999999999999</v>
+        <v>5.96</v>
       </c>
       <c r="L36" t="n">
         <v>5.96</v>
@@ -2493,7 +2924,7 @@
         <v>3.72</v>
       </c>
       <c r="N36" t="n">
-        <v>2.55</v>
+        <v>3.93</v>
       </c>
       <c r="O36" t="n">
         <v>3.76</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>10.81</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>10215</v>
+        <v>12277.5</v>
       </c>
       <c r="I37" t="n">
         <v>11532.15219172315</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>26.3</v>
+        <v>11.42</v>
       </c>
       <c r="L37" t="n">
         <v>4.26</v>
       </c>
       <c r="M37" t="n">
-        <v>1.93</v>
+        <v>12.03</v>
       </c>
       <c r="N37" t="n">
-        <v>7.81</v>
+        <v>20.19</v>
       </c>
       <c r="O37" t="n">
         <v>-3.93</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>24.15</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45702.55208333334</v>
+        <v>45705.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>11209</v>
+        <v>10751.85</v>
       </c>
       <c r="I38" t="n">
         <v>10773.93203380939</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K38" t="n">
-        <v>-8.699999999999999</v>
+        <v>-12.43</v>
       </c>
       <c r="L38" t="n">
-        <v>10.31</v>
+        <v>12.84</v>
       </c>
       <c r="M38" t="n">
         <v>4.7</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>16.39</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45719.55208333334</v>
+        <v>45720.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>11777</v>
+        <v>12225</v>
       </c>
       <c r="I39" t="n">
         <v>11995.25549815383</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>-9.529999999999999</v>
+        <v>-13.7</v>
       </c>
       <c r="L39" t="n">
-        <v>11.78</v>
+        <v>14.5</v>
       </c>
       <c r="M39" t="n">
         <v>0.68</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.75</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45727.38541666666</v>
+        <v>45727.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>12291.95</v>
+        <v>12150</v>
       </c>
       <c r="I40" t="n">
         <v>12208.92189861477</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>0.55</v>
+        <v>-0.61</v>
       </c>
       <c r="L40" t="n">
         <v>6.13</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.4</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>12000</v>
+        <v>12763</v>
       </c>
       <c r="I41" t="n">
         <v>12480.25800637095</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>31</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>1.23</v>
+        <v>-5.05</v>
       </c>
       <c r="L41" t="n">
         <v>9.26</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>13.41</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45813.55208333334</v>
+        <v>45814.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>19511</v>
+        <v>18353</v>
       </c>
       <c r="I42" t="n">
         <v>18478.76217548184</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K42" t="n">
-        <v>52.87</v>
+        <v>43.8</v>
       </c>
       <c r="L42" t="n">
         <v>5.48</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.83</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45825.38541666666</v>
+        <v>45825.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>18338</v>
+        <v>18590</v>
       </c>
       <c r="I43" t="n">
         <v>18501.73611972015</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>0.08</v>
+        <v>-1.29</v>
       </c>
       <c r="L43" t="n">
         <v>7.61</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45849.38541666666</v>
+        <v>45849.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>18670</v>
+        <v>18600</v>
       </c>
       <c r="I44" t="n">
         <v>18622.01006929728</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>0.43</v>
+        <v>0.05</v>
       </c>
       <c r="L44" t="n">
         <v>2.76</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.24</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45859.55208333334</v>
+        <v>45860.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>19300</v>
+        <v>20000</v>
       </c>
       <c r="I45" t="n">
         <v>19768.71706261927</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.76</v>
+        <v>-7.53</v>
       </c>
       <c r="L45" t="n">
-        <v>6.34</v>
+        <v>8.31</v>
       </c>
       <c r="M45" t="n">
         <v>0.87</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.94</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45891.55208333334</v>
+        <v>45894.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>19860</v>
+        <v>19450</v>
       </c>
       <c r="I46" t="n">
         <v>19483.9424662382</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.7</v>
+        <v>-2.75</v>
       </c>
       <c r="L46" t="n">
         <v>6.15</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45912.38541666666</v>
+        <v>45912.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>19671</v>
+        <v>19905</v>
       </c>
       <c r="I47" t="n">
         <v>19898.63610602516</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.14</v>
+        <v>-2.34</v>
       </c>
       <c r="L47" t="n">
         <v>4.29</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45918.55208333334</v>
+        <v>45919.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>19326</v>
+        <v>19026</v>
       </c>
       <c r="I48" t="n">
         <v>19038.10155655265</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.91</v>
+        <v>-4.42</v>
       </c>
       <c r="L48" t="n">
-        <v>3.04</v>
+        <v>4.51</v>
       </c>
       <c r="M48" t="n">
         <v>0.01</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45959.55208333334</v>
+        <v>45960.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>17506</v>
+        <v>17962</v>
       </c>
       <c r="I49" t="n">
         <v>17554.47704471328</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K49" t="n">
-        <v>7.99</v>
+        <v>5.59</v>
       </c>
       <c r="L49" t="n">
         <v>3.95</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.54</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45994.55208333334</v>
+        <v>45995.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>21785</v>
+        <v>20415</v>
       </c>
       <c r="I50" t="n">
         <v>21430.34550931221</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K50" t="n">
-        <v>21.28</v>
+        <v>13.66</v>
       </c>
       <c r="L50" t="n">
         <v>3.8</v>
@@ -3291,7 +3890,7 @@
         <v>0.83</v>
       </c>
       <c r="N50" t="n">
-        <v>4.16</v>
+        <v>7.83</v>
       </c>
       <c r="O50" t="n">
         <v>2.39</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.27</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46028.55208333334</v>
+        <v>46029.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>18824</v>
+        <v>19810</v>
       </c>
       <c r="I51" t="n">
         <v>19296.09524013425</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K51" t="n">
-        <v>7.79</v>
+        <v>2.96</v>
       </c>
       <c r="L51" t="n">
         <v>6.81</v>
@@ -3348,7 +3959,7 @@
         <v>0.83</v>
       </c>
       <c r="N51" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="O51" t="n">
         <v>-7.83</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>8.9</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46030.38541666666</v>
+        <v>46030.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>19589</v>
+        <v>18388</v>
       </c>
       <c r="I52" t="n">
         <v>18396.38469049148</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.12</v>
+        <v>-7.18</v>
       </c>
       <c r="L52" t="n">
-        <v>5.5</v>
+        <v>7.85</v>
       </c>
       <c r="M52" t="n">
         <v>0.3</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>11.43</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46050.38541666666</v>
+        <v>46050.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>17509</v>
+        <v>17685</v>
       </c>
       <c r="I53" t="n">
         <v>17666.73155535299</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>4.78</v>
+        <v>3.82</v>
       </c>
       <c r="L53" t="n">
         <v>6.94</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>25555</v>
+        <v>24325</v>
       </c>
       <c r="I54" t="n">
         <v>24350.99932796542</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>33</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K54" t="n">
-        <v>44.5</v>
+        <v>37.55</v>
       </c>
       <c r="L54" t="n">
         <v>1.57</v>
@@ -3519,7 +4166,7 @@
         <v>3.95</v>
       </c>
       <c r="N54" t="n">
-        <v>3.84</v>
+        <v>4.52</v>
       </c>
       <c r="O54" t="n">
         <v>5.05</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>24930</v>
+        <v>25995</v>
       </c>
       <c r="I55" t="n">
         <v>25856.93242080779</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.49</v>
+        <v>-6.87</v>
       </c>
       <c r="L55" t="n">
         <v>8.220000000000001</v>
@@ -3576,7 +4235,7 @@
         <v>3.61</v>
       </c>
       <c r="N55" t="n">
-        <v>4.1</v>
+        <v>4.17</v>
       </c>
       <c r="O55" t="n">
         <v>-4.52</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>32650</v>
+        <v>32570</v>
       </c>
       <c r="I56" t="n">
         <v>32600.59667039171</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K56" t="n">
-        <v>25.6</v>
+        <v>25.29</v>
       </c>
       <c r="L56" t="n">
         <v>3.27</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.04</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46161.55208333334</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>33060</v>
+        <v>35355</v>
       </c>
       <c r="I57" t="n">
         <v>34425.30673340007</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.5</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>3.56</v>
+        <v>9</v>
       </c>
       <c r="M57" t="n">
         <v>1.2</v>
       </c>
       <c r="N57" t="n">
-        <v>1.61</v>
+        <v>7.99</v>
       </c>
       <c r="O57" t="n">
         <v>-1.56</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>11.87</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>36355</v>
+        <v>35055</v>
       </c>
       <c r="I58" t="n">
         <v>35301.04188553089</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K58" t="n">
-        <v>2.83</v>
+        <v>-0.85</v>
       </c>
       <c r="L58" t="n">
         <v>7.48</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>11.34</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46190.55208333334</v>
+        <v>46191.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>35950</v>
+        <v>36150</v>
       </c>
       <c r="I59" t="n">
         <v>36052.95913116793</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.55</v>
+        <v>-3.12</v>
       </c>
       <c r="L59" t="n">
         <v>6.8</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>7.78</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46197.38541666666</v>
+        <v>46197.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>34560</v>
+        <v>33840</v>
       </c>
       <c r="I60" t="n">
         <v>34554.52477582739</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.4</v>
+        <v>-6.39</v>
       </c>
       <c r="L60" t="n">
-        <v>5.06</v>
+        <v>6.83</v>
       </c>
       <c r="M60" t="n">
         <v>0.62</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46241.55208333334</v>
+        <v>46244.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>32600</v>
+        <v>36040</v>
       </c>
       <c r="I61" t="n">
         <v>33008.25507865274</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>44</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K61" t="n">
-        <v>3.66</v>
+        <v>-6.5</v>
       </c>
       <c r="L61" t="n">
-        <v>4.95</v>
+        <v>6.6</v>
       </c>
       <c r="M61" t="n">
-        <v>1.74</v>
+        <v>7.36</v>
       </c>
       <c r="N61" t="n">
-        <v>4.58</v>
+        <v>10.89</v>
       </c>
       <c r="O61" t="n">
         <v>-6.42</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>9.65</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46253.38541666666</v>
+        <v>46253.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>33750</v>
+        <v>33500</v>
       </c>
       <c r="I62" t="n">
         <v>33681.71901886231</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.35</v>
+        <v>-7.05</v>
       </c>
       <c r="L62" t="n">
-        <v>6.77</v>
+        <v>7.44</v>
       </c>
       <c r="M62" t="n">
         <v>0.47</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.27</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>31200</v>
+        <v>31975</v>
       </c>
       <c r="I63" t="n">
         <v>31724.77216235581</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>6.87</v>
+        <v>4.55</v>
       </c>
       <c r="L63" t="n">
         <v>4.4</v>
@@ -4032,7 +4787,7 @@
         <v>1.83</v>
       </c>
       <c r="N63" t="n">
-        <v>3.21</v>
+        <v>3.56</v>
       </c>
       <c r="O63" t="n">
         <v>-5</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>6.15</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>31100</v>
+        <v>30230</v>
       </c>
       <c r="I64" t="n">
         <v>30344.28822476546</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.74</v>
+        <v>-5.46</v>
       </c>
       <c r="L64" t="n">
-        <v>4.22</v>
+        <v>5.66</v>
       </c>
       <c r="M64" t="n">
-        <v>-0</v>
+        <v>0.34</v>
       </c>
       <c r="N64" t="n">
-        <v>1.43</v>
+        <v>3.34</v>
       </c>
       <c r="O64" t="n">
         <v>3.56</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.86</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>31545</v>
+        <v>31815</v>
       </c>
       <c r="I65" t="n">
         <v>31701.22590044739</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.35</v>
+        <v>-5.24</v>
       </c>
       <c r="L65" t="n">
         <v>5.9</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.07</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>31200</v>
+        <v>29895</v>
       </c>
       <c r="I66" t="n">
         <v>30069.70603553921</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.93</v>
+        <v>-6.03</v>
       </c>
       <c r="L66" t="n">
-        <v>5.85</v>
+        <v>7.02</v>
       </c>
       <c r="M66" t="n">
-        <v>0.62</v>
+        <v>2.21</v>
       </c>
       <c r="N66" t="n">
-        <v>2.08</v>
+        <v>3.09</v>
       </c>
       <c r="O66" t="n">
         <v>0.38</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,12 @@
       <c r="Q67" t="n">
         <v>20</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>119.8</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.2</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="11">
@@ -6455,7 +7264,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.34</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7284,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7294,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>77.04000000000001</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7304,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.4</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7314,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.49</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7324,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.95</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="21">
@@ -6525,7 +7334,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.84</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="22">
@@ -6535,7 +7344,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7354,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7364,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="25">
@@ -6565,7 +7374,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.71</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="26">
@@ -6575,7 +7384,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.51</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7394,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.15</v>
+        <v>20.19</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7404,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
